--- a/VerveStacks_JPN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_JPN_grids_kan/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jeragroup.sharepoint.com/sites/JE_Ltd1114_JA010/DocLib1/4. 各種モデル/3. エネルギー需給モデル/03_Vervestacks Model/vervestacks_models/VerveStacks_JPN_grids_kan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F5143E-E697-4339-8A39-F17C88A9DA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{D5F5143E-E697-4339-8A39-F17C88A9DA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32541F33-3C3F-40FB-8DCC-D3580930A5B0}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13800" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -2454,32 +2454,32 @@
   <numFmts count="15">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_(&quot;£&quot;* #,##0.00_);_(&quot;£&quot;* \(#,##0.00\);_(&quot;£&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;kr&quot;\ * #,##0_ ;_ &quot;kr&quot;\ * \-#,##0_ ;_ &quot;kr&quot;\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_ &quot;kr&quot;\ * #,##0.00_ ;_ &quot;kr&quot;\ * \-#,##0.00_ ;_ &quot;kr&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="[&gt;0.5]#,##0;[&lt;-0.5]\-#,##0;\-"/>
-    <numFmt numFmtId="170" formatCode="_-[$€-2]* #,##0.00_-;\-[$€-2]* #,##0.00_-;_-[$€-2]* &quot;-&quot;??_-"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0\ &quot;F&quot;_-;\-* #,##0\ &quot;F&quot;_-;_-* &quot;-&quot;\ &quot;F&quot;_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0\ _F_-;\-* #,##0\ _F_-;_-* &quot;-&quot;\ _F_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0.00\ &quot;F&quot;_-;\-* #,##0.00\ &quot;F&quot;_-;_-* &quot;-&quot;??\ &quot;F&quot;_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="_-* #,##0.00\ _F_-;\-* #,##0.00\ _F_-;_-* &quot;-&quot;??\ _F_-;_-@_-"/>
-    <numFmt numFmtId="175" formatCode="#,##0.0;\-#,##0.0;&quot;-&quot;"/>
-    <numFmt numFmtId="176" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="176" formatCode="_(&quot;£&quot;* #,##0.00_);_(&quot;£&quot;* \(#,##0.00\);_(&quot;£&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ &quot;kr&quot;\ * #,##0_ ;_ &quot;kr&quot;\ * \-#,##0_ ;_ &quot;kr&quot;\ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;kr&quot;\ * #,##0.00_ ;_ &quot;kr&quot;\ * \-#,##0.00_ ;_ &quot;kr&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="181" formatCode="[&gt;0.5]#,##0;[&lt;-0.5]\-#,##0;\-"/>
+    <numFmt numFmtId="182" formatCode="_-[$€-2]* #,##0.00_-;\-[$€-2]* #,##0.00_-;_-[$€-2]* &quot;-&quot;??_-"/>
+    <numFmt numFmtId="183" formatCode="_-* #,##0\ &quot;F&quot;_-;\-* #,##0\ &quot;F&quot;_-;_-* &quot;-&quot;\ &quot;F&quot;_-;_-@_-"/>
+    <numFmt numFmtId="184" formatCode="_-* #,##0\ _F_-;\-* #,##0\ _F_-;_-* &quot;-&quot;\ _F_-;_-@_-"/>
+    <numFmt numFmtId="185" formatCode="_-* #,##0.00\ &quot;F&quot;_-;\-* #,##0.00\ &quot;F&quot;_-;_-* &quot;-&quot;??\ &quot;F&quot;_-;_-@_-"/>
+    <numFmt numFmtId="186" formatCode="_-* #,##0.00\ _F_-;\-* #,##0.00\ _F_-;_-* &quot;-&quot;??\ _F_-;_-@_-"/>
+    <numFmt numFmtId="187" formatCode="#,##0.0;\-#,##0.0;&quot;-&quot;"/>
+    <numFmt numFmtId="188" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2487,7 +2487,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2495,21 +2495,21 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2743,7 +2743,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2751,7 +2751,7 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2759,28 +2759,28 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2800,6 +2800,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2833,19 +2834,26 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3094,6 +3102,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3440,7 +3454,7 @@
     <xf numFmtId="0" fontId="15" fillId="35" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3448,8 +3462,8 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="35" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3481,8 +3495,8 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="1" fillId="42" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="43" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="43" borderId="0"/>
@@ -3508,68 +3522,68 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3602,10 +3616,10 @@
     <xf numFmtId="0" fontId="10" fillId="45" borderId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="0">
+    <xf numFmtId="181" fontId="36" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="0">
+    <xf numFmtId="181" fontId="36" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3634,10 +3648,10 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="47" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -3797,8 +3811,8 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3817,9 +3831,9 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="35" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="35" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="36" borderId="6"/>
@@ -3906,7 +3920,7 @@
     <xf numFmtId="0" fontId="28" fillId="46" borderId="12">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="4" fontId="38" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -3918,13 +3932,12 @@
     <xf numFmtId="0" fontId="57" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="188" fontId="3" fillId="0" borderId="2" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="431"/>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="22" xfId="432" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="432" applyBorder="1"/>
@@ -3944,6 +3957,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="234"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="234" applyNumberFormat="1"/>
+    <xf numFmtId="188" fontId="2" fillId="47" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="437">
     <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{822ECCD2-03B4-4EB0-AADE-6DECEB39BB19}"/>
@@ -4130,9 +4145,7 @@
     <cellStyle name="Good 2" xfId="182" xr:uid="{63196ABB-E7F7-4631-B61C-58ACAB42E00D}"/>
     <cellStyle name="Heading" xfId="183" xr:uid="{AE639CE0-6CBC-49AB-A0BE-AD3F8827E219}"/>
     <cellStyle name="Heading 1 2" xfId="184" xr:uid="{2D9A63A6-BB28-4750-950F-E3B35810EF9B}"/>
-    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
     <cellStyle name="Heading 2 2" xfId="185" xr:uid="{2EFF7F87-AB7A-425D-84EB-90B6535D5C59}"/>
-    <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Heading 3 2" xfId="186" xr:uid="{EE469C21-B1A7-46DF-8FCA-2CE06A5BA6BA}"/>
     <cellStyle name="Heading 4 2" xfId="187" xr:uid="{7C8F4F2B-0269-4086-93E8-CD4D28426D71}"/>
     <cellStyle name="Heading 5" xfId="188" xr:uid="{DA6AF693-BB50-49A8-BB30-17AB31FF52DE}"/>
@@ -4160,7 +4173,6 @@
     <cellStyle name="Neutral 2" xfId="211" xr:uid="{0BD2AEA9-BAC5-48AA-B1A7-8F95AAE6853E}"/>
     <cellStyle name="Neutral 2 2" xfId="435" xr:uid="{773FC3D2-CB25-40C1-9022-B7616488FC25}"/>
     <cellStyle name="Neutral 3" xfId="210" xr:uid="{2435363D-5388-4D62-AE78-289118217843}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="212" xr:uid="{347F5622-C417-4F2E-B072-ECA7EBFFEE51}"/>
     <cellStyle name="Normal 10 2" xfId="213" xr:uid="{18DCF291-6F11-4BCE-B818-75EBA1AE6458}"/>
     <cellStyle name="Normal 10 2 2" xfId="214" xr:uid="{6EA27B8E-717D-469B-A557-382261907D98}"/>
@@ -4383,6 +4395,9 @@
     <cellStyle name="Valuutta_Layo9704" xfId="426" xr:uid="{C8483C0B-1B44-4263-B519-BFBB23191117}"/>
     <cellStyle name="Warning Text 2" xfId="427" xr:uid="{455BF35A-338D-443D-867E-478F2F3BEB22}"/>
     <cellStyle name="Обычный_2++_CRFReport-template" xfId="428" xr:uid="{2BCF8D67-4912-44A4-9A34-06400FC197EF}"/>
+    <cellStyle name="見出し 2" xfId="1" builtinId="17"/>
+    <cellStyle name="見出し 3" xfId="2" builtinId="18"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4794,15 +4809,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="16.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.53125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.9140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -4853,6 +4868,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4861,20 +4877,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:R109"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.25" customWidth="1"/>
+    <col min="16" max="16" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.58203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="17.649999999999999" thickBot="1">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="2:18" ht="22" thickBot="1">
+      <c r="B3" s="22" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="2"/>
@@ -4884,7 +4906,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="22" t="s">
         <v>8</v>
       </c>
       <c r="N3" s="2"/>
@@ -4892,44 +4914,44 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:18" ht="15" thickTop="1" thickBot="1">
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="2:18" ht="19" thickTop="1" thickBot="1">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="R4" t="s">
@@ -7262,6 +7284,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:C334">
     <sortCondition ref="C19:C334"/>
   </sortState>
+  <phoneticPr fontId="59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7269,276 +7292,277 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3984375" style="6"/>
-    <col min="4" max="4" width="14.1328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.86328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.3984375" style="6"/>
+    <col min="1" max="1" width="9.1640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.4140625" style="5"/>
+    <col min="4" max="4" width="14.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.4140625" style="5"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:7">
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2022</v>
       </c>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14.25">
-      <c r="B12" s="7" t="s">
+    <row r="12" spans="2:7" ht="14.5">
+      <c r="B12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="8" t="str">
+      <c r="E12" s="7" t="str">
         <f>"msy"&amp;COUNT(E14:E46)&amp;"_"&amp;MAX(E14:E46)</f>
         <v>msy7_2050</v>
       </c>
-      <c r="F12" s="8" t="str">
+      <c r="F12" s="7" t="str">
         <f t="shared" ref="F12:G12" si="0">"msy"&amp;COUNT(F14:F45)&amp;"_"&amp;MAX(F14:F45)</f>
         <v>msy6_2050</v>
       </c>
-      <c r="G12" s="8" t="str">
+      <c r="G12" s="7" t="str">
         <f t="shared" si="0"/>
         <v>msy5_2050</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14.25">
-      <c r="B13" s="9">
+    <row r="13" spans="2:7" ht="14.5">
+      <c r="B13" s="8">
         <v>1</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14.25">
-      <c r="B14" s="9">
+    <row r="14" spans="2:7" ht="14.5">
+      <c r="B14" s="8">
         <v>5</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <f t="shared" ref="E14:G14" si="1">$B$4</f>
         <v>2022</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <f t="shared" si="1"/>
         <v>2022</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <f t="shared" si="1"/>
         <v>2022</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14.25">
-      <c r="B15" s="9">
+    <row r="15" spans="2:7" ht="14.5">
+      <c r="B15" s="8">
         <v>5</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="5">
         <f>E14+3</f>
         <v>2025</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <f>F14+3</f>
         <v>2025</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <f>G14+3</f>
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14.25">
-      <c r="B16" s="9">
+    <row r="16" spans="2:7" ht="14.5">
+      <c r="B16" s="8">
         <v>10</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="5">
         <f>E15+5</f>
         <v>2030</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <f>F15+5</f>
         <v>2030</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <f>G15+5</f>
         <v>2030</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14.25">
-      <c r="B17" s="9">
+    <row r="17" spans="2:7" ht="14.5">
+      <c r="B17" s="8">
         <v>10</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="5">
         <f t="shared" ref="E17:E20" si="2">E16+5</f>
         <v>2035</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="5">
         <f>F16+5</f>
         <v>2035</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <f>G16+10</f>
         <v>2040</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14.25">
-      <c r="B18" s="9">
+    <row r="18" spans="2:7" ht="14.5">
+      <c r="B18" s="8">
         <v>10</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <f t="shared" si="2"/>
         <v>2040</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <f>F17+5</f>
         <v>2040</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <f t="shared" ref="G18" si="3">G17+10</f>
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.25">
-      <c r="B19" s="9">
+    <row r="19" spans="2:7" ht="14.5">
+      <c r="B19" s="8">
         <v>10</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <f t="shared" si="2"/>
         <v>2045</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <f>F18+10</f>
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14.25">
-      <c r="B20" s="9">
+    <row r="20" spans="2:7" ht="14.5">
+      <c r="B20" s="8">
         <v>10</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <f t="shared" si="2"/>
         <v>2050</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="14.25">
-      <c r="B21" s="9">
+    <row r="21" spans="2:7" ht="14.5">
+      <c r="B21" s="8">
         <v>10</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.25">
-      <c r="B22" s="9">
+    <row r="22" spans="2:7" ht="14.5">
+      <c r="B22" s="8">
         <v>10</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.25">
-      <c r="B23" s="9">
+    <row r="23" spans="2:7" ht="14.5">
+      <c r="B23" s="8">
         <v>10</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14.25">
-      <c r="B24" s="9">
+    <row r="24" spans="2:7" ht="14.5">
+      <c r="B24" s="8">
         <v>10</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14.25">
-      <c r="B25" s="9"/>
-      <c r="D25" s="6" t="s">
+    <row r="25" spans="2:7" ht="14.5">
+      <c r="B25" s="8"/>
+      <c r="D25" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14.25">
-      <c r="B26" s="9"/>
-      <c r="D26" s="6" t="s">
+    <row r="26" spans="2:7" ht="14.5">
+      <c r="B26" s="8"/>
+      <c r="D26" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14.25">
-      <c r="B27" s="9"/>
-      <c r="D27" s="6" t="s">
+    <row r="27" spans="2:7" ht="14.5">
+      <c r="B27" s="8"/>
+      <c r="D27" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14.25">
-      <c r="B28" s="9"/>
-      <c r="D28" s="6" t="s">
+    <row r="28" spans="2:7" ht="14.5">
+      <c r="B28" s="8"/>
+      <c r="D28" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="14.25">
-      <c r="B29" s="9"/>
-      <c r="D29" s="6" t="s">
+    <row r="29" spans="2:7" ht="14.5">
+      <c r="B29" s="8"/>
+      <c r="D29" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14.25">
-      <c r="B30" s="9"/>
-    </row>
-    <row r="31" spans="2:7" ht="14.25">
-      <c r="B31" s="9"/>
-    </row>
-    <row r="32" spans="2:7" ht="14.25">
-      <c r="B32" s="9"/>
-    </row>
-    <row r="33" spans="2:2" ht="14.25">
-      <c r="B33" s="9"/>
+    <row r="30" spans="2:7" ht="14.5">
+      <c r="B30" s="8"/>
+    </row>
+    <row r="31" spans="2:7" ht="14.5">
+      <c r="B31" s="8"/>
+    </row>
+    <row r="32" spans="2:7" ht="14.5">
+      <c r="B32" s="8"/>
+    </row>
+    <row r="33" spans="2:2" ht="14.5">
+      <c r="B33" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -7547,10 +7571,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7176EA-6692-4715-959C-084A5DC4D5A9}">
   <dimension ref="B3:H191"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="3" spans="2:8">
-      <c r="B3" t="s">
+      <c r="B3" s="23" t="s">
         <v>426</v>
       </c>
     </row>
@@ -11879,6 +11912,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11886,248 +11920,248 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
   <dimension ref="B1:N42"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="11"/>
-    <col min="2" max="2" width="8.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.46484375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.46484375" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.53125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.3984375" style="11"/>
+    <col min="1" max="1" width="11.4140625" style="10"/>
+    <col min="2" max="2" width="8.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.9140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.9140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.4140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="12.75">
-      <c r="B1" s="6"/>
-      <c r="C1" s="10"/>
-    </row>
-    <row r="2" spans="2:12" ht="12.75">
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="2:12" ht="12.75">
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
+    <row r="1" spans="2:12" ht="12.5">
+      <c r="B1" s="5"/>
+      <c r="C1" s="9"/>
+    </row>
+    <row r="2" spans="2:12" ht="12.5">
+      <c r="B2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" spans="2:12" ht="12.5">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="15" t="s">
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="2:12" ht="12">
+      <c r="B5" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>0</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>0</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>0</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>0</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>0</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:12">
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <v>0</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="15" t="s">
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" spans="2:12" ht="12">
+      <c r="B15" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="14" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <v>2222</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="10" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="17" spans="2:14">
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <v>8888</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="12.75">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-    </row>
-    <row r="19" spans="2:14" ht="12.75">
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-    </row>
-    <row r="20" spans="2:14" ht="12.75">
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="2:14" ht="14.25">
+    <row r="18" spans="2:14" ht="12.5">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+    </row>
+    <row r="19" spans="2:14" ht="12.5">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+    </row>
+    <row r="20" spans="2:14" ht="12.5">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+    </row>
+    <row r="21" spans="2:14" ht="18">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -12142,7 +12176,7 @@
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="2:14" ht="14.25">
+    <row r="22" spans="2:14" ht="18">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -12157,7 +12191,7 @@
       <c r="M22"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="2:14" ht="14.25">
+    <row r="23" spans="2:14" ht="18">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -12172,7 +12206,7 @@
       <c r="M23"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="2:14" ht="14.25">
+    <row r="24" spans="2:14" ht="18">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -12187,7 +12221,7 @@
       <c r="M24"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="2:14" ht="14.25">
+    <row r="25" spans="2:14" ht="18">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
@@ -12202,7 +12236,7 @@
       <c r="M25"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="2:14" ht="14.25">
+    <row r="26" spans="2:14" ht="18">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
@@ -12217,7 +12251,7 @@
       <c r="M26"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="2:14" ht="14.25">
+    <row r="27" spans="2:14" ht="18">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
@@ -12232,7 +12266,7 @@
       <c r="M27"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="2:14" ht="14.25">
+    <row r="28" spans="2:14" ht="18">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
@@ -12247,7 +12281,7 @@
       <c r="M28"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="2:14" ht="14.25">
+    <row r="29" spans="2:14" ht="18">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
@@ -12262,7 +12296,7 @@
       <c r="M29"/>
       <c r="N29"/>
     </row>
-    <row r="30" spans="2:14" ht="14.25">
+    <row r="30" spans="2:14" ht="18">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
@@ -12277,7 +12311,7 @@
       <c r="M30"/>
       <c r="N30"/>
     </row>
-    <row r="31" spans="2:14" ht="14.25">
+    <row r="31" spans="2:14" ht="18">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
@@ -12292,7 +12326,7 @@
       <c r="M31"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="2:14" ht="14.25">
+    <row r="32" spans="2:14" ht="18">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
@@ -12307,7 +12341,7 @@
       <c r="M32"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="2:14" ht="14.25">
+    <row r="33" spans="2:14" ht="18">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
@@ -12322,7 +12356,7 @@
       <c r="M33"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="2:14" ht="14.25">
+    <row r="34" spans="2:14" ht="18">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
@@ -12337,7 +12371,7 @@
       <c r="M34"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="2:14" ht="14.25">
+    <row r="35" spans="2:14" ht="18">
       <c r="B35"/>
       <c r="C35"/>
       <c r="D35"/>
@@ -12352,7 +12386,7 @@
       <c r="M35"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="2:14" ht="14.25">
+    <row r="36" spans="2:14" ht="18">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
@@ -12367,7 +12401,7 @@
       <c r="M36"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="2:14" ht="14.25">
+    <row r="37" spans="2:14" ht="18">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -12382,7 +12416,7 @@
       <c r="M37"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="2:14" ht="14.25">
+    <row r="38" spans="2:14" ht="18">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -12397,7 +12431,7 @@
       <c r="M38"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="2:14" ht="14.25">
+    <row r="39" spans="2:14" ht="18">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -12412,7 +12446,7 @@
       <c r="M39"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="2:14" ht="14.25">
+    <row r="40" spans="2:14" ht="18">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -12427,7 +12461,7 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="2:14" ht="14.25">
+    <row r="41" spans="2:14" ht="18">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -12442,7 +12476,7 @@
       <c r="M41"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="2:14" ht="14.25">
+    <row r="42" spans="2:14" ht="18">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -12458,6 +12492,7 @@
       <c r="N42"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
@@ -12467,1638 +12502,1639 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
   <dimension ref="A2:N102"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="11.4140625" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="11"/>
-    <col min="2" max="2" width="12.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.3984375" style="11"/>
-    <col min="5" max="5" width="13.53125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.3984375" style="11"/>
-    <col min="12" max="12" width="17.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.3984375" style="11"/>
+    <col min="1" max="1" width="11.4140625" style="10"/>
+    <col min="2" max="2" width="12.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.4140625" style="10"/>
+    <col min="5" max="5" width="13.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.58203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.4140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.9140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.4140625" style="10"/>
+    <col min="12" max="12" width="17.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.4140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="17.649999999999999" thickBot="1">
-      <c r="A2" s="13"/>
-      <c r="B2" s="20" t="s">
+    <row r="2" spans="1:14" ht="22" thickBot="1">
+      <c r="A2" s="12"/>
+      <c r="B2" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="4" t="s">
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" ht="19" thickTop="1" thickBot="1">
+      <c r="A3" s="12"/>
+      <c r="B3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>2022</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.15">
-      <c r="A4" s="13"/>
-      <c r="B4" s="19" t="s">
+    <row r="4" spans="1:14" ht="16.5">
+      <c r="A4" s="12"/>
+      <c r="B4" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="F4" s="11" t="s">
+      <c r="C4" s="5"/>
+      <c r="F4" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="10">
         <v>0.05</v>
       </c>
-      <c r="J4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="6" t="s">
+      <c r="J4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="5">
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.15">
-      <c r="A5" s="13"/>
-      <c r="B5" s="19" t="s">
+    <row r="5" spans="1:14" ht="16.5">
+      <c r="A5" s="12"/>
+      <c r="B5" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <v>1</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="6" t="s">
+      <c r="J5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="5">
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.15">
-      <c r="A6" s="13"/>
-      <c r="B6" s="19" t="s">
+    <row r="6" spans="1:14" ht="16.5">
+      <c r="A6" s="12"/>
+      <c r="B6" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="10">
         <v>2025</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="5">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.15">
-      <c r="A7" s="13"/>
-      <c r="B7" s="19" t="s">
+    <row r="7" spans="1:14" ht="16.5">
+      <c r="A7" s="12"/>
+      <c r="B7" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="10">
         <v>1</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="5">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.15">
-      <c r="A8" s="13"/>
-      <c r="B8" s="19" t="s">
+    <row r="8" spans="1:14" ht="16.5">
+      <c r="A8" s="12"/>
+      <c r="B8" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="10">
         <v>2.2201</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="5">
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.15">
-      <c r="A9" s="13"/>
-      <c r="B9" s="19" t="s">
+    <row r="9" spans="1:14" ht="16.5">
+      <c r="A9" s="12"/>
+      <c r="B9" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <v>2.1427</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="5">
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.15">
-      <c r="A10" s="13"/>
-      <c r="B10" s="19" t="s">
+    <row r="10" spans="1:14" ht="16.5">
+      <c r="A10" s="12"/>
+      <c r="B10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="10">
         <v>2.077</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="5">
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.15">
-      <c r="A11" s="13"/>
-      <c r="B11" s="19" t="s">
+    <row r="11" spans="1:14" ht="16.5">
+      <c r="A11" s="12"/>
+      <c r="B11" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="10">
         <v>2.0358000000000001</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="5">
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.15">
-      <c r="A12" s="13"/>
-      <c r="B12" s="19" t="s">
+    <row r="12" spans="1:14" ht="16.5">
+      <c r="A12" s="12"/>
+      <c r="B12" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <v>1.9870000000000001</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="5">
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.15">
-      <c r="A13" s="13"/>
-      <c r="B13" s="19" t="s">
+    <row r="13" spans="1:14" ht="16.5">
+      <c r="A13" s="12"/>
+      <c r="B13" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="10">
         <v>1.9192</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="5">
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.15">
-      <c r="A14" s="13"/>
-      <c r="B14" s="19" t="s">
+    <row r="14" spans="1:14" ht="16.5">
+      <c r="A14" s="12"/>
+      <c r="B14" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="10">
         <v>1.8468</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="5">
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.15">
-      <c r="A15" s="13"/>
-      <c r="B15" s="19" t="s">
+    <row r="15" spans="1:14" ht="16.5">
+      <c r="A15" s="12"/>
+      <c r="B15" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="10">
         <v>1.7799</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="5">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.15">
-      <c r="A16" s="13"/>
-      <c r="B16" s="19" t="s">
+    <row r="16" spans="1:14" ht="16.5">
+      <c r="A16" s="12"/>
+      <c r="B16" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="10">
         <v>1.722</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="5">
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.15">
-      <c r="A17" s="13"/>
-      <c r="B17" s="19" t="s">
+    <row r="17" spans="1:14" ht="16.5">
+      <c r="A17" s="12"/>
+      <c r="B17" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="10">
         <v>1.6836</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="5">
         <v>37.68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.15">
-      <c r="B18" s="19" t="s">
+    <row r="18" spans="1:14" ht="16.5">
+      <c r="B18" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="10">
         <v>1.6446000000000001</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="5">
         <v>2139.4548</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.15">
-      <c r="B19" s="19" t="s">
+    <row r="19" spans="1:14" ht="16.5">
+      <c r="B19" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="10">
         <v>1.6102000000000001</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="M19" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="5">
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.15">
-      <c r="B20" s="19" t="s">
+    <row r="20" spans="1:14" ht="16.5">
+      <c r="B20" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="10">
         <v>1.5770999999999999</v>
       </c>
-      <c r="L20" s="6" t="s">
+      <c r="L20" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="M20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="5">
         <v>3.6</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.15">
-      <c r="B21" s="19" t="s">
+    <row r="21" spans="1:14" ht="16.5">
+      <c r="B21" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="10">
         <v>1.5488</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.15">
-      <c r="B22" s="19" t="s">
+    <row r="22" spans="1:14" ht="16.5">
+      <c r="B22" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="10">
         <v>1.5224</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="5">
         <v>31.536000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.15">
-      <c r="B23" s="19" t="s">
+    <row r="23" spans="1:14" ht="16.5">
+      <c r="B23" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="10">
         <v>1.5058</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.15">
-      <c r="B24" s="19" t="s">
+    <row r="24" spans="1:14" ht="16.5">
+      <c r="B24" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="10">
         <v>1.4844999999999999</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="10">
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.15">
-      <c r="B25" s="19" t="s">
+    <row r="25" spans="1:14" ht="16.5">
+      <c r="B25" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="10">
         <v>1.4518</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M25" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="10">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.15">
-      <c r="B26" s="19" t="s">
+    <row r="26" spans="1:14" ht="16.5">
+      <c r="B26" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="10">
         <v>1.4198999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.15">
-      <c r="B27" s="19" t="s">
+    <row r="27" spans="1:14" ht="16.5">
+      <c r="B27" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="10">
         <v>1.3986000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.15">
-      <c r="B28" s="19" t="s">
+    <row r="28" spans="1:14" ht="16.5">
+      <c r="B28" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="10">
         <v>1.3727</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.15">
-      <c r="B29" s="19" t="s">
+    <row r="29" spans="1:14" ht="16.5">
+      <c r="B29" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="10">
         <v>1.3369</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.15">
-      <c r="B30" s="19" t="s">
+    <row r="30" spans="1:14" ht="16.5">
+      <c r="B30" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="10">
         <v>1.2967</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.15">
-      <c r="B31" s="19" t="s">
+    <row r="31" spans="1:14" ht="16.5">
+      <c r="B31" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="10">
         <v>1.2583</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.15">
-      <c r="B32" s="19" t="s">
+    <row r="32" spans="1:14" ht="16.5">
+      <c r="B32" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="10">
         <v>1.2253000000000001</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="13.15">
-      <c r="B33" s="19" t="s">
+    <row r="33" spans="2:9" ht="16.5">
+      <c r="B33" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="10">
         <v>1.2023999999999999</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="13.15">
-      <c r="B34" s="19" t="s">
+    <row r="34" spans="2:9" ht="16.5">
+      <c r="B34" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="10">
         <v>1.1931</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="13.15">
-      <c r="B35" s="19" t="s">
+    <row r="35" spans="2:9" ht="16.5">
+      <c r="B35" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="10">
         <v>1.1793</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="13.15">
-      <c r="B36" s="19" t="s">
+    <row r="36" spans="2:9" ht="16.5">
+      <c r="B36" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="10">
         <v>1.1552</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="13.15">
-      <c r="B37" s="19" t="s">
+    <row r="37" spans="2:9" ht="16.5">
+      <c r="B37" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="10">
         <v>1.1334</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="13.15">
-      <c r="B38" s="19" t="s">
+    <row r="38" spans="2:9" ht="16.5">
+      <c r="B38" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="10">
         <v>1.1136999999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="13.15">
-      <c r="B39" s="19" t="s">
+    <row r="39" spans="2:9" ht="16.5">
+      <c r="B39" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="10">
         <v>1.0934999999999999</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="13.15">
-      <c r="B40" s="19" t="s">
+    <row r="40" spans="2:9" ht="16.5">
+      <c r="B40" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="10">
         <v>1.0831</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="13.15">
-      <c r="B41" s="19" t="s">
+    <row r="41" spans="2:9" ht="16.5">
+      <c r="B41" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="10">
         <v>1.0719000000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="13.15">
-      <c r="B42" s="19" t="s">
+    <row r="42" spans="2:9" ht="16.5">
+      <c r="B42" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42" s="10">
         <v>1.0519000000000001</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="13.15">
-      <c r="B43" s="19" t="s">
+    <row r="43" spans="2:9" ht="16.5">
+      <c r="B43" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="10">
         <v>1.0274000000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="13.15">
-      <c r="B44" s="19" t="s">
+    <row r="44" spans="2:9" ht="16.5">
+      <c r="B44" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="10">
         <v>1.0091000000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="13.15">
-      <c r="B45" s="19" t="s">
+    <row r="45" spans="2:9" ht="16.5">
+      <c r="B45" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="13.15">
-      <c r="B46" s="19" t="s">
+    <row r="46" spans="2:9" ht="16.5">
+      <c r="B46" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="10">
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="13.15">
-      <c r="B47" s="19" t="s">
+    <row r="47" spans="2:9" ht="16.5">
+      <c r="B47" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G47" s="11" t="s">
+      <c r="G47" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="10">
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="13.15">
-      <c r="B48" s="19" t="s">
+    <row r="48" spans="2:9" ht="16.5">
+      <c r="B48" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="10">
         <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="13.15">
-      <c r="B49" s="19" t="s">
+    <row r="49" spans="2:9" ht="16.5">
+      <c r="B49" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="G49" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="H49" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="10">
         <v>0.94910000000000005</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="13.15">
-      <c r="B50" s="19" t="s">
+    <row r="50" spans="2:9" ht="16.5">
+      <c r="B50" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G50" s="11" t="s">
+      <c r="G50" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="10">
         <v>0.92969999999999997</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.15">
-      <c r="B51" s="19" t="s">
+    <row r="51" spans="2:9" ht="16.5">
+      <c r="B51" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F51" s="11" t="str">
+      <c r="F51" s="10" t="str">
         <f>F46</f>
         <v>G_CUREX</v>
       </c>
-      <c r="G51" s="11" t="str">
+      <c r="G51" s="10" t="str">
         <f t="shared" ref="G51:I51" si="0">G46</f>
         <v>USD20</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="10">
         <f t="shared" si="0"/>
         <v>0.98960000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="13.15">
-      <c r="B52" s="19" t="s">
+    <row r="52" spans="2:9" ht="16.5">
+      <c r="B52" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="13.15">
-      <c r="B53" s="19" t="s">
+    <row r="53" spans="2:9" ht="16.5">
+      <c r="B53" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="13.15">
-      <c r="B54" s="19" t="s">
+    <row r="54" spans="2:9" ht="16.5">
+      <c r="B54" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9">
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="56" spans="2:9">
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9">
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="I57" s="11">
+      <c r="I57" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="58" spans="2:9">
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="I58" s="11">
+      <c r="I58" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="59" spans="2:9">
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="I59" s="11">
+      <c r="I59" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="60" spans="2:9">
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="I60" s="11">
+      <c r="I60" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="61" spans="2:9">
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I61" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="62" spans="2:9">
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I62" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="63" spans="2:9">
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="I63" s="11">
+      <c r="I63" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="64" spans="2:9">
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="I64" s="11">
+      <c r="I64" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="65" spans="6:9">
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="I65" s="11">
+      <c r="I65" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="66" spans="6:9">
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="I66" s="11">
+      <c r="I66" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="67" spans="6:9">
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="I67" s="11">
+      <c r="I67" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="68" spans="6:9">
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I68" s="11">
+      <c r="I68" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="69" spans="6:9">
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I69" s="11">
+      <c r="I69" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="70" spans="6:9">
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I70" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="71" spans="6:9">
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I71" s="11">
+      <c r="I71" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="72" spans="6:9">
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="I72" s="11">
+      <c r="I72" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="73" spans="6:9">
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I73" s="11">
+      <c r="I73" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="74" spans="6:9">
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I74" s="11">
+      <c r="I74" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="75" spans="6:9">
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="I75" s="11">
+      <c r="I75" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="76" spans="6:9">
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="I76" s="11">
+      <c r="I76" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="77" spans="6:9">
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="I77" s="11">
+      <c r="I77" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="78" spans="6:9">
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="I78" s="11">
+      <c r="I78" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="79" spans="6:9">
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="I79" s="11">
+      <c r="I79" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="80" spans="6:9">
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="I80" s="11">
+      <c r="I80" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="81" spans="6:9">
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="I81" s="11">
+      <c r="I81" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="82" spans="6:9">
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="I82" s="11">
+      <c r="I82" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="83" spans="6:9">
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H83" s="11" t="s">
+      <c r="H83" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="I83" s="11">
+      <c r="I83" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="84" spans="6:9">
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="I84" s="11">
+      <c r="I84" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="85" spans="6:9">
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="I85" s="11">
+      <c r="I85" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="86" spans="6:9">
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I86" s="11">
+      <c r="I86" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="87" spans="6:9">
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="H87" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="I87" s="11">
+      <c r="I87" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="88" spans="6:9">
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H88" s="11" t="s">
+      <c r="H88" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="I88" s="11">
+      <c r="I88" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="89" spans="6:9">
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H89" s="11" t="s">
+      <c r="H89" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="I89" s="11">
+      <c r="I89" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="90" spans="6:9">
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="I90" s="11">
+      <c r="I90" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="91" spans="6:9">
-      <c r="F91" s="11" t="s">
+      <c r="F91" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H91" s="11" t="s">
+      <c r="H91" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="I91" s="11">
+      <c r="I91" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="92" spans="6:9">
-      <c r="F92" s="11" t="s">
+      <c r="F92" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H92" s="11" t="s">
+      <c r="H92" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="I92" s="11">
+      <c r="I92" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="93" spans="6:9">
-      <c r="F93" s="11" t="s">
+      <c r="F93" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="I93" s="11">
+      <c r="I93" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="94" spans="6:9">
-      <c r="F94" s="11" t="s">
+      <c r="F94" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="I94" s="11">
+      <c r="I94" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="95" spans="6:9">
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="H95" s="11" t="str">
+      <c r="H95" s="10" t="str">
         <f>H51</f>
         <v>USD21_alt</v>
       </c>
-      <c r="I95" s="11">
+      <c r="I95" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="5:10" ht="17.649999999999999" thickBot="1">
-      <c r="E99" s="20" t="s">
+    <row r="99" spans="5:10" ht="22" thickBot="1">
+      <c r="E99" s="19" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
-      <c r="E100" s="4" t="s">
+    <row r="100" spans="5:10" ht="19" thickTop="1" thickBot="1">
+      <c r="E100" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F100" s="4" t="s">
+      <c r="F100" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H100" s="4" t="s">
+      <c r="H100" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I100" s="4">
+      <c r="I100" s="3">
         <v>2022</v>
       </c>
-      <c r="J100" s="4" t="s">
+      <c r="J100" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="101" spans="5:10" ht="14.25">
+    <row r="101" spans="5:10" ht="18">
       <c r="E101"/>
-      <c r="F101" s="21" t="s">
+      <c r="F101" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="G101" s="21" t="s">
+      <c r="G101" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="H101" s="21" t="s">
+      <c r="H101" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I101" s="22">
+      <c r="I101" s="21">
         <f>1.10926234054354*I40</f>
         <v>1.201442041042708</v>
       </c>
     </row>
-    <row r="102" spans="5:10" ht="14.25">
+    <row r="102" spans="5:10" ht="18">
       <c r="E102"/>
-      <c r="F102" s="21" t="s">
+      <c r="F102" s="20" t="s">
         <v>192</v>
       </c>
       <c r="G102"/>
-      <c r="H102" s="21" t="s">
+      <c r="H102" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I102" s="22">
+      <c r="I102" s="21">
         <f>I84</f>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -14107,278 +14143,545 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE1F0D2-7682-484B-9627-54FDDA96E26C}">
   <dimension ref="B3:D33"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="2" width="8.86328125" style="6"/>
-    <col min="3" max="3" width="20.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.86328125" style="6"/>
+    <col min="1" max="2" width="8.83203125" style="5"/>
+    <col min="3" max="3" width="20.4140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.649999999999999" thickBot="1">
-      <c r="B3" s="20" t="s">
+    <row r="3" spans="2:4" ht="22" thickBot="1">
+      <c r="B3" s="19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="2:4" ht="19" thickTop="1" thickBot="1">
+      <c r="B4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>-1</v>
       </c>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
-      <c r="B23" s="18" t="s">
+    <row r="23" spans="2:4" ht="13">
+      <c r="B23" s="17" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="2:4" ht="17.649999999999999" thickBot="1">
-      <c r="B25" s="20" t="s">
+    <row r="25" spans="2:4" ht="22" thickBot="1">
+      <c r="B25" s="19" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
-      <c r="B26" s="4" t="s">
+    <row r="26" spans="2:4" ht="19" thickTop="1" thickBot="1">
+      <c r="B26" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="30" spans="2:4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="31" spans="2:4">
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="32" spans="2:4">
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>176</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="59"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="961b6814-c230-4269-82bd-def8d4313a06">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bab054b8-c314-4c35-aaad-e6094b2a3aec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101002DB47EE0E92B004DA587A5AC06BCAB72" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="cff8d2101153e857ff4355cc66cd45e5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="961b6814-c230-4269-82bd-def8d4313a06" xmlns:ns3="bab054b8-c314-4c35-aaad-e6094b2a3aec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a602de66b0b03817e42d2b6948bbd6d9" ns2:_="" ns3:_="">
+    <xsd:import namespace="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <xsd:import namespace="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="961b6814-c230-4269-82bd-def8d4313a06" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="761ec606-d3f6-431d-aca1-879ead0541e3" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="20" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="bab054b8-c314-4c35-aaad-e6094b2a3aec" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fd7fabe0-2dba-4629-88b9-b2647f7a99db}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="bab054b8-c314-4c35-aaad-e6094b2a3aec">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{524AE411-643E-4BA2-A4D9-4AC9289C4CC4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <ds:schemaRef ds:uri="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83A9BA7A-9DD1-425E-945C-66F2333CEDF9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFB4AB35-02ED-4533-BFE8-21315DEF5733}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="961b6814-c230-4269-82bd-def8d4313a06"/>
+    <ds:schemaRef ds:uri="bab054b8-c314-4c35-aaad-e6094b2a3aec"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>